--- a/uploads/bulk_upload/excelFile/finance bulkupload format with auto cus_id.xlsx
+++ b/uploads/bulk_upload/excelFile/finance bulkupload format with auto cus_id.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="75" windowWidth="24915" windowHeight="12600"/>
@@ -11,15 +11,12 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="99">
-  <si>
-    <t>cus_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="112">
   <si>
     <t>cus_name</t>
   </si>
@@ -285,9 +282,6 @@
     <t>rrr</t>
   </si>
   <si>
-    <t>Monthly</t>
-  </si>
-  <si>
     <t>Vandavasi</t>
   </si>
   <si>
@@ -300,9 +294,6 @@
     <t>Existing</t>
   </si>
   <si>
-    <t>U-102</t>
-  </si>
-  <si>
     <t>Mother</t>
   </si>
   <si>
@@ -313,16 +304,64 @@
   </si>
   <si>
     <t>Male</t>
+  </si>
+  <si>
+    <t>how to know</t>
+  </si>
+  <si>
+    <t>loan count</t>
+  </si>
+  <si>
+    <t>first loan date</t>
+  </si>
+  <si>
+    <t>travel with company</t>
+  </si>
+  <si>
+    <t>monthly income</t>
+  </si>
+  <si>
+    <t>Other income</t>
+  </si>
+  <si>
+    <t>support income</t>
+  </si>
+  <si>
+    <t>monthly due capacity</t>
+  </si>
+  <si>
+    <t>Commitment</t>
+  </si>
+  <si>
+    <t>Ganga</t>
+  </si>
+  <si>
+    <t>Customer Reference</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t>Monthlt</t>
+  </si>
+  <si>
+    <t>EMI</t>
+  </si>
+  <si>
+    <t>After Benefit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,7 +520,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -516,7 +554,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -692,9 +729,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:BZ29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
@@ -703,91 +740,99 @@
     <col min="6" max="6" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.5703125" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" customWidth="1"/>
-    <col min="28" max="28" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="16.28515625" customWidth="1"/>
-    <col min="40" max="40" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="11" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="44" max="47" width="15.42578125" customWidth="1"/>
-    <col min="48" max="48" width="20.7109375" customWidth="1"/>
-    <col min="49" max="49" width="25.5703125" customWidth="1"/>
-    <col min="50" max="50" width="19.28515625" customWidth="1"/>
-    <col min="51" max="51" width="16.140625" customWidth="1"/>
-    <col min="52" max="52" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.5703125" customWidth="1"/>
-    <col min="54" max="54" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="12" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12" customWidth="1"/>
-    <col min="58" max="58" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.5703125" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" customWidth="1"/>
+    <col min="27" max="27" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.85546875" customWidth="1"/>
+    <col min="30" max="30" width="20.140625" customWidth="1"/>
+    <col min="31" max="31" width="18" customWidth="1"/>
+    <col min="32" max="32" width="18.140625" customWidth="1"/>
+    <col min="33" max="33" width="18.42578125" customWidth="1"/>
+    <col min="34" max="34" width="22.85546875" customWidth="1"/>
+    <col min="35" max="35" width="16.28515625" customWidth="1"/>
+    <col min="36" max="36" width="18.28515625" customWidth="1"/>
+    <col min="37" max="37" width="20.42578125" customWidth="1"/>
+    <col min="38" max="38" width="10" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="11" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="16.28515625" customWidth="1"/>
+    <col min="48" max="48" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="55" width="15.42578125" customWidth="1"/>
+    <col min="56" max="56" width="20.7109375" customWidth="1"/>
+    <col min="57" max="57" width="25.5703125" customWidth="1"/>
+    <col min="58" max="58" width="19.28515625" customWidth="1"/>
+    <col min="59" max="59" width="16.140625" customWidth="1"/>
     <col min="60" max="60" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="61" max="62" width="13.5703125" customWidth="1"/>
-    <col min="63" max="63" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.5703125" customWidth="1"/>
+    <col min="62" max="62" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="12" bestFit="1" customWidth="1"/>
-    <col min="65" max="67" width="12" customWidth="1"/>
-    <col min="68" max="68" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="12" customWidth="1"/>
+    <col min="66" max="66" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="15.140625" customWidth="1"/>
+    <col min="68" max="68" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="70" width="13.5703125" customWidth="1"/>
+    <col min="71" max="71" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="12" bestFit="1" customWidth="1"/>
+    <col min="73" max="75" width="12" customWidth="1"/>
+    <col min="76" max="76" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:78" ht="15.75" thickBot="1">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>0</v>
       </c>
       <c r="J1" t="s">
         <v>7</v>
@@ -808,10 +853,10 @@
         <v>12</v>
       </c>
       <c r="P1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q1" t="s">
         <v>13</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>61</v>
       </c>
       <c r="R1" t="s">
         <v>14</v>
@@ -847,133 +892,157 @@
         <v>24</v>
       </c>
       <c r="AC1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL1" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AM1" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AN1" t="s">
         <v>27</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AO1" t="s">
         <v>28</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AP1" t="s">
         <v>29</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AQ1" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AR1" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AS1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT1" t="s">
         <v>32</v>
       </c>
-      <c r="AK1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AL1" t="s">
+      <c r="AU1" t="s">
         <v>33</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AV1" t="s">
         <v>34</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AW1" t="s">
         <v>35</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AX1" t="s">
         <v>36</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AY1" t="s">
         <v>37</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AZ1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BA1" t="s">
         <v>38</v>
       </c>
-      <c r="AR1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AS1" t="s">
+      <c r="BB1" t="s">
         <v>39</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BC1" t="s">
         <v>40</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BD1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BE1" t="s">
         <v>41</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BF1" t="s">
+        <v>42</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>43</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>44</v>
+      </c>
+      <c r="BI1" t="s">
         <v>63</v>
       </c>
-      <c r="AW1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AZ1" t="s">
+      <c r="BJ1" t="s">
         <v>45</v>
       </c>
-      <c r="BA1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BB1" t="s">
+      <c r="BK1" t="s">
         <v>46</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BL1" t="s">
         <v>47</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BM1" t="s">
+        <v>77</v>
+      </c>
+      <c r="BN1" t="s">
         <v>48</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BO1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BP1" t="s">
         <v>78</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BQ1" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>81</v>
+      </c>
+      <c r="BS1" t="s">
         <v>49</v>
       </c>
-      <c r="BG1" t="s">
-        <v>80</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>79</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>81</v>
-      </c>
-      <c r="BJ1" t="s">
+      <c r="BT1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>84</v>
+      </c>
+      <c r="BV1" t="s">
         <v>82</v>
       </c>
-      <c r="BK1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BL1" t="s">
+      <c r="BW1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BX1" t="s">
         <v>51</v>
       </c>
-      <c r="BM1" t="s">
-        <v>85</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>83</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>84</v>
-      </c>
-      <c r="BP1" t="s">
+      <c r="BY1" t="s">
         <v>52</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BZ1" t="s">
         <v>53</v>
       </c>
-      <c r="BR1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:78" ht="15.75" thickBot="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -981,10 +1050,10 @@
         <v>902532889254</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2">
         <v>37233</v>
@@ -996,142 +1065,167 @@
         <v>9876512342</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="J2" t="s">
+        <v>90</v>
       </c>
       <c r="K2" t="s">
-        <v>92</v>
-      </c>
-      <c r="L2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="1">
+        <v>589432889254</v>
+      </c>
+      <c r="M2">
+        <v>8798798798</v>
+      </c>
+      <c r="N2">
+        <v>76</v>
+      </c>
+      <c r="O2" t="s">
         <v>66</v>
       </c>
-      <c r="M2" s="1">
-        <v>589432889254</v>
-      </c>
-      <c r="N2">
-        <v>8798798798</v>
-      </c>
-      <c r="O2">
-        <v>76</v>
-      </c>
       <c r="P2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" t="s">
         <v>67</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>62</v>
       </c>
       <c r="R2" t="s">
         <v>68</v>
       </c>
       <c r="S2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T2" t="s">
-        <v>69</v>
-      </c>
-      <c r="U2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB2">
+        <v>890000</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>3000</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>10000</v>
+      </c>
+      <c r="AL2" t="s">
         <v>56</v>
       </c>
-      <c r="Z2" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC2">
+      <c r="AM2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN2">
+        <v>76000</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AU2" s="4"/>
+      <c r="AV2">
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <v>22</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>450000</v>
+      </c>
+      <c r="BA2">
         <v>890000</v>
       </c>
-      <c r="AD2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF2">
-        <v>76000</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="BB2">
+        <v>908000</v>
+      </c>
+      <c r="BC2">
+        <v>786</v>
+      </c>
+      <c r="BD2">
+        <v>450</v>
+      </c>
+      <c r="BE2">
+        <v>567</v>
+      </c>
+      <c r="BF2">
+        <v>98000</v>
+      </c>
+      <c r="BG2" s="2">
+        <v>45849</v>
+      </c>
+      <c r="BH2" s="2">
+        <v>45850</v>
+      </c>
+      <c r="BI2" s="2">
+        <v>37481</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>70</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>71</v>
+      </c>
+      <c r="BO2">
+        <v>890000</v>
+      </c>
+      <c r="BP2">
+        <v>890000</v>
+      </c>
+      <c r="BS2" s="1">
+        <v>98787678676897</v>
+      </c>
+      <c r="BT2">
+        <v>32456566766</v>
+      </c>
+      <c r="BX2" s="2">
+        <v>45849</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>74</v>
+      </c>
+      <c r="BZ2" t="s">
         <v>65</v>
       </c>
-      <c r="AK2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM2" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN2">
-        <v>1</v>
-      </c>
-      <c r="AO2">
-        <v>22</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>450000</v>
-      </c>
-      <c r="AS2">
-        <v>890000</v>
-      </c>
-      <c r="AT2">
-        <v>908000</v>
-      </c>
-      <c r="AU2">
-        <v>786</v>
-      </c>
-      <c r="AV2">
-        <v>450</v>
-      </c>
-      <c r="AW2">
-        <v>567</v>
-      </c>
-      <c r="AX2">
-        <v>98000</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>45484</v>
-      </c>
-      <c r="AZ2" s="2">
-        <v>45485</v>
-      </c>
-      <c r="BA2" s="2">
-        <v>37481</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>71</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>86</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>72</v>
-      </c>
-      <c r="BG2">
-        <v>890000</v>
-      </c>
-      <c r="BH2">
-        <v>890000</v>
-      </c>
-      <c r="BK2" s="1">
-        <v>98787678676897</v>
-      </c>
-      <c r="BL2">
-        <v>32456566766</v>
-      </c>
-      <c r="BP2" s="2">
-        <v>45572</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>75</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:78" ht="15.75" thickBot="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1139,10 +1233,10 @@
         <v>994248402222</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2">
         <v>37233</v>
@@ -1154,283 +1248,277 @@
         <v>9876512342</v>
       </c>
       <c r="H3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
         <v>94</v>
       </c>
       <c r="J3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="1">
+        <v>890989089096</v>
+      </c>
+      <c r="M3">
+        <v>8798798798</v>
+      </c>
+      <c r="N3">
+        <v>76</v>
+      </c>
+      <c r="O3" t="s">
         <v>66</v>
       </c>
-      <c r="M3" s="1">
-        <v>890989089096</v>
-      </c>
-      <c r="N3">
-        <v>8798798798</v>
-      </c>
-      <c r="O3">
-        <v>76</v>
-      </c>
       <c r="P3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q3" t="s">
         <v>67</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>62</v>
       </c>
       <c r="R3" t="s">
         <v>68</v>
       </c>
       <c r="S3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T3" t="s">
-        <v>69</v>
-      </c>
-      <c r="U3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB3">
+        <v>890000</v>
+      </c>
+      <c r="AL3" t="s">
         <v>56</v>
       </c>
-      <c r="Z3" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC3">
+      <c r="AM3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN3">
+        <v>76000</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV3">
+        <v>1</v>
+      </c>
+      <c r="AW3">
+        <v>22</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>450000</v>
+      </c>
+      <c r="BA3">
         <v>890000</v>
       </c>
-      <c r="AD3" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF3">
-        <v>76000</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM3" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AN3">
-        <v>1</v>
-      </c>
-      <c r="AO3">
-        <v>22</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>450000</v>
-      </c>
-      <c r="AS3">
-        <v>890000</v>
-      </c>
-      <c r="AT3">
+      <c r="BB3">
         <v>908000</v>
       </c>
-      <c r="AU3">
+      <c r="BC3">
         <v>786</v>
       </c>
-      <c r="AV3">
+      <c r="BD3">
         <v>450</v>
       </c>
-      <c r="AW3">
+      <c r="BE3">
         <v>567</v>
       </c>
-      <c r="AX3">
+      <c r="BF3">
         <v>98000</v>
       </c>
-      <c r="AY3" s="2">
+      <c r="BG3" s="2">
         <v>45484</v>
       </c>
-      <c r="AZ3" s="2">
+      <c r="BH3" s="2">
         <v>45485</v>
       </c>
-      <c r="BA3" s="2">
+      <c r="BI3" s="2">
         <v>37481</v>
       </c>
-      <c r="BB3" t="s">
+      <c r="BJ3" t="s">
+        <v>70</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN3" t="s">
         <v>71</v>
       </c>
-      <c r="BE3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>72</v>
-      </c>
-      <c r="BG3">
+      <c r="BO3">
         <v>60000</v>
       </c>
-      <c r="BH3">
+      <c r="BP3">
         <v>90000</v>
       </c>
-      <c r="BK3" s="1">
+      <c r="BS3" s="1">
         <v>98765454564544</v>
       </c>
-      <c r="BL3">
+      <c r="BT3">
         <v>9999999999</v>
       </c>
-      <c r="BP3" s="2">
+      <c r="BX3" s="2">
         <v>45572</v>
       </c>
-      <c r="BQ3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="BY3" t="s">
+        <v>93</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:78">
       <c r="B4" s="1"/>
       <c r="E4" s="2"/>
-      <c r="M4" s="1"/>
-      <c r="AY4" s="2"/>
-      <c r="AZ4" s="2"/>
-      <c r="BA4" s="2"/>
-      <c r="BP4" s="2"/>
-    </row>
-    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L4" s="1"/>
+      <c r="BG4" s="2"/>
+      <c r="BH4" s="2"/>
+      <c r="BI4" s="2"/>
+      <c r="BX4" s="2"/>
+    </row>
+    <row r="5" spans="1:78">
       <c r="B5" s="1"/>
       <c r="E5" s="2"/>
-      <c r="M5" s="1"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BK5" s="1"/>
-      <c r="BP5" s="2"/>
-    </row>
-    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L5" s="1"/>
+      <c r="BG5" s="2"/>
+      <c r="BH5" s="2"/>
+      <c r="BI5" s="2"/>
+      <c r="BS5" s="1"/>
+      <c r="BX5" s="2"/>
+    </row>
+    <row r="6" spans="1:78">
       <c r="B6" s="1"/>
       <c r="E6" s="2"/>
-      <c r="M6" s="1"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BK6" s="1"/>
-      <c r="BP6" s="2"/>
-    </row>
-    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L6" s="1"/>
+      <c r="BG6" s="2"/>
+      <c r="BH6" s="2"/>
+      <c r="BI6" s="2"/>
+      <c r="BS6" s="1"/>
+      <c r="BX6" s="2"/>
+    </row>
+    <row r="7" spans="1:78">
       <c r="B7" s="1"/>
       <c r="E7" s="2"/>
-      <c r="M7" s="1"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BK7" s="1"/>
-      <c r="BP7" s="2"/>
-    </row>
-    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L7" s="1"/>
+      <c r="BG7" s="2"/>
+      <c r="BH7" s="2"/>
+      <c r="BI7" s="2"/>
+      <c r="BS7" s="1"/>
+      <c r="BX7" s="2"/>
+    </row>
+    <row r="8" spans="1:78">
       <c r="B8" s="1"/>
       <c r="E8" s="2"/>
-      <c r="M8" s="1"/>
-      <c r="AY8" s="2"/>
-      <c r="AZ8" s="2"/>
-      <c r="BA8" s="2"/>
-      <c r="BK8" s="1"/>
-      <c r="BP8" s="2"/>
-    </row>
-    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L8" s="1"/>
+      <c r="BG8" s="2"/>
+      <c r="BH8" s="2"/>
+      <c r="BI8" s="2"/>
+      <c r="BS8" s="1"/>
+      <c r="BX8" s="2"/>
+    </row>
+    <row r="9" spans="1:78">
       <c r="B9" s="1"/>
       <c r="E9" s="2"/>
-      <c r="M9" s="1"/>
-      <c r="AY9" s="2"/>
-      <c r="AZ9" s="2"/>
-      <c r="BA9" s="2"/>
-      <c r="BK9" s="1"/>
-      <c r="BP9" s="2"/>
-    </row>
-    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L9" s="1"/>
+      <c r="BG9" s="2"/>
+      <c r="BH9" s="2"/>
+      <c r="BI9" s="2"/>
+      <c r="BS9" s="1"/>
+      <c r="BX9" s="2"/>
+    </row>
+    <row r="10" spans="1:78">
       <c r="B10" s="1"/>
       <c r="E10" s="2"/>
-      <c r="M10" s="1"/>
-      <c r="AY10" s="2"/>
-      <c r="AZ10" s="2"/>
-      <c r="BA10" s="2"/>
-      <c r="BK10" s="1"/>
-      <c r="BP10" s="2"/>
-    </row>
-    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L10" s="1"/>
+      <c r="BG10" s="2"/>
+      <c r="BH10" s="2"/>
+      <c r="BI10" s="2"/>
+      <c r="BS10" s="1"/>
+      <c r="BX10" s="2"/>
+    </row>
+    <row r="11" spans="1:78">
       <c r="B11" s="1"/>
       <c r="E11" s="2"/>
-      <c r="M11" s="1"/>
-      <c r="AY11" s="2"/>
-      <c r="AZ11" s="2"/>
-      <c r="BA11" s="2"/>
-      <c r="BP11" s="2"/>
-    </row>
-    <row r="12" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L11" s="1"/>
+      <c r="BG11" s="2"/>
+      <c r="BH11" s="2"/>
+      <c r="BI11" s="2"/>
+      <c r="BX11" s="2"/>
+    </row>
+    <row r="12" spans="1:78">
       <c r="B12" s="1"/>
       <c r="E12" s="2"/>
-      <c r="M12" s="1"/>
-      <c r="AY12" s="2"/>
-      <c r="AZ12" s="2"/>
-      <c r="BA12" s="2"/>
-      <c r="BP12" s="2"/>
-    </row>
-    <row r="13" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="L12" s="1"/>
+      <c r="BG12" s="2"/>
+      <c r="BH12" s="2"/>
+      <c r="BI12" s="2"/>
+      <c r="BX12" s="2"/>
+    </row>
+    <row r="13" spans="1:78">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:78">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:78">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:70" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:78">
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2">
       <c r="B17" s="1"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2">
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" s="1"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2">
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2">
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2">
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2">
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2">
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2">
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2">
       <c r="B29" s="1"/>
     </row>
   </sheetData>
@@ -1440,18 +1528,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
